--- a/artfynd/A 19726-2023 artfynd.xlsx
+++ b/artfynd/A 19726-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122652265</v>
       </c>
       <c r="B2" t="n">
-        <v>58012</v>
+        <v>58013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>122652263</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 19726-2023 artfynd.xlsx
+++ b/artfynd/A 19726-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122652263</v>
+        <v>122652265</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>58107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122652265</v>
+        <v>122652263</v>
       </c>
       <c r="B3" t="n">
-        <v>58107</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,37 +811,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102125</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 19726-2023 artfynd.xlsx
+++ b/artfynd/A 19726-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122652265</v>
+        <v>122652263</v>
       </c>
       <c r="B2" t="n">
-        <v>58107</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102125</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122652263</v>
+        <v>122652265</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>58107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,37 +811,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102125</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
